--- a/data/Final_markes.xlsx
+++ b/data/Final_markes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,33 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2/10  Poorly written and disorganized.</t>
+          <t>2/10
+Insufficient and disorganized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>assignment_CTV2_text</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4/10
+Partial understanding; needs significant improvement in clarity and structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ayush_Kumar_Resume(LLumo)_text</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>My apologies.  I assumed from the previous response that it was handwritten.  Please provide the typed text.</t>
         </is>
       </c>
     </row>

--- a/data/Final_markes.xlsx
+++ b/data/Final_markes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,32 +449,7 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>2/10
-Insufficient and disorganized.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>assignment_CTV2_text</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>4/10
-Partial understanding; needs significant improvement in clarity and structure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ayush_Kumar_Resume(LLumo)_text</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>My apologies.  I assumed from the previous response that it was handwritten.  Please provide the typed text.</t>
+Poor grammar and structure.</t>
         </is>
       </c>
     </row>

--- a/data/Final_markes.xlsx
+++ b/data/Final_markes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,8 +448,33 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2/10
-Poor grammar and structure.</t>
+          <t>4/10
+Insufficient detail and poor structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>assignment_CTV2_text</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5/10
+Some understanding shown, but lacks depth and clarity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ayushResume_text</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>My apologies.  I am an AI and do not process images.  I was responding based on the assumption that you had provided handwritten answers previously.  Please provide the typed answers so I can evaluate them.</t>
         </is>
       </c>
     </row>

--- a/data/Final_markes.xlsx
+++ b/data/Final_markes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,8 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4/10
-Insufficient detail and poor structure.</t>
+          <t>2/10  Incoherent and incomplete.</t>
         </is>
       </c>
     </row>
@@ -461,8 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5/10
-Some understanding shown, but lacks depth and clarity.</t>
+          <t>4/10.  Answers are simplistic and lack depth.</t>
         </is>
       </c>
     </row>
@@ -474,7 +472,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>My apologies.  I am an AI and do not process images.  I was responding based on the assumption that you had provided handwritten answers previously.  Please provide the typed answers so I can evaluate them.</t>
+          <t>Please provide the answers to the questions so I can evaluate them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>IMG_20240724_221056_text</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8/10. Good overview, but some explanations could be more concise and examples are occasionally missing crucial context.</t>
         </is>
       </c>
     </row>
